--- a/tests/workbooktests/workbooks/test_calendars.xlsx
+++ b/tests/workbooktests/workbooks/test_calendars.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3BE3D4-09CA-453E-AA10-BD49B0C634BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9690DD57-097D-4671-A599-AB72DE620844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
+    <workbookView xWindow="-4560" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="types" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="89">
   <si>
     <t>ARGENTINA</t>
   </si>
@@ -289,14 +311,43 @@
   </si>
   <si>
     <t>US_SOFR</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar2</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar3</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendarN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -324,13 +375,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -346,9 +398,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -386,7 +438,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -492,7 +544,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -643,13 +695,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3075420B-A904-48C0-8CC0-21FB5C882A54}">
   <dimension ref="B2:C50"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.109375" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -658,7 +710,7 @@
         <v>Buenos Aires stock exchange</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -667,7 +719,7 @@
         <v>Australia settlement</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -676,7 +728,7 @@
         <v>Austrian settlement</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -685,7 +737,7 @@
         <v>Botswana</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -694,7 +746,7 @@
         <v>Brazil</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -703,7 +755,7 @@
         <v>Canada</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -712,7 +764,7 @@
         <v>Santiago Stock Exchange</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -721,7 +773,7 @@
         <v>Shanghai stock exchange</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -730,7 +782,7 @@
         <v>Prague stock exchange</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
@@ -739,7 +791,7 @@
         <v>Denmark</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -748,7 +800,7 @@
         <v>Finland</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -757,7 +809,7 @@
         <v>French settlement</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -766,7 +818,7 @@
         <v>Frankfurt stock exchange</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -775,7 +827,7 @@
         <v>Hong Kong stock exchange</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -784,7 +836,7 @@
         <v>Hungary</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
@@ -793,7 +845,7 @@
         <v>Iceland stock exchange</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -802,7 +854,7 @@
         <v>National Stock Exchange of India</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>17</v>
       </c>
@@ -811,7 +863,7 @@
         <v>Jakarta stock exchange</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>18</v>
       </c>
@@ -820,7 +872,7 @@
         <v>Tel Aviv stock exchange</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>19</v>
       </c>
@@ -829,7 +881,7 @@
         <v>Italian settlement</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>20</v>
       </c>
@@ -838,7 +890,7 @@
         <v>Japan</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>21</v>
       </c>
@@ -847,7 +899,7 @@
         <v>Mexican stock exchange</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>22</v>
       </c>
@@ -856,7 +908,7 @@
         <v>New Zealand (Wellington)</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>23</v>
       </c>
@@ -865,7 +917,7 @@
         <v>Norway</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -874,7 +926,7 @@
         <v>Poland Settlement</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>25</v>
       </c>
@@ -883,7 +935,7 @@
         <v>Bucharest stock exchange</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>26</v>
       </c>
@@ -892,7 +944,7 @@
         <v>Russian settlement</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>27</v>
       </c>
@@ -901,7 +953,7 @@
         <v>Tadawul</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>28</v>
       </c>
@@ -910,7 +962,7 @@
         <v>Singapore exchange</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
@@ -919,7 +971,7 @@
         <v>Bratislava stock exchange</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
@@ -928,7 +980,7 @@
         <v>South Africa</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>31</v>
       </c>
@@ -937,7 +989,7 @@
         <v>South-Korea exchange</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>32</v>
       </c>
@@ -946,7 +998,7 @@
         <v>Sweden</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>33</v>
       </c>
@@ -955,7 +1007,7 @@
         <v>Switzerland</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>34</v>
       </c>
@@ -964,7 +1016,7 @@
         <v>Taiwan stock exchange</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>35</v>
       </c>
@@ -973,7 +1025,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>36</v>
       </c>
@@ -982,7 +1034,7 @@
         <v>Thailand stock exchange</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>37</v>
       </c>
@@ -991,7 +1043,7 @@
         <v>Turkey</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>38</v>
       </c>
@@ -1000,7 +1052,7 @@
         <v>Ukrainian stock exchange</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>39</v>
       </c>
@@ -1009,7 +1061,7 @@
         <v>New York stock exchange</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>40</v>
       </c>
@@ -1018,7 +1070,7 @@
         <v>UK settlement</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>41</v>
       </c>
@@ -1027,7 +1079,7 @@
         <v>Null</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>42</v>
       </c>
@@ -1036,7 +1088,7 @@
         <v>weekends only</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>78</v>
       </c>
@@ -1045,7 +1097,7 @@
         <v>UK settlement</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>79</v>
       </c>
@@ -1054,7 +1106,7 @@
         <v>US settlement</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>80</v>
       </c>
@@ -1063,7 +1115,7 @@
         <v>Federal Reserve Bankwire System</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>81</v>
       </c>
@@ -1081,13 +1133,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33850488-5007-411C-8F3E-026395460888}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -1096,7 +1148,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1104,7 +1156,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1113,7 +1165,7 @@
         <v>FRIDAY</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -1121,7 +1173,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1136,13 +1188,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E6" t="b">
         <f>_xll.qlCalendarIsHoliday(B1,D5)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -1151,7 +1203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1160,7 +1212,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -1169,7 +1221,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1178,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -1187,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1196,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1205,16 +1257,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
       <c r="B14">
         <f>_xll.qlCalendarBusinessDaysBetween(B1,B4,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
@@ -1223,7 +1275,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -1232,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -1241,13 +1293,13 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>55</v>
       </c>
       <c r="B19" s="1">
         <f>TRANSPOSE(_xll.qlCalendarBusinessDayList(B1,B4,B5))</f>
-        <v>46027</v>
+        <v>46024</v>
       </c>
     </row>
   </sheetData>
@@ -1259,12 +1311,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41849B37-CA87-4E4A-8B76-B839138C7508}">
   <dimension ref="A2:C18"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.44140625" customWidth="1"/>
+    <col min="1" max="1" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1273,7 +1325,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -1281,7 +1333,7 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -1289,7 +1341,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1297,7 +1349,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -1305,7 +1357,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1314,7 +1366,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1323,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1333,10 +1385,10 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1345,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1354,10 +1406,10 @@
         <v>46024</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1366,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -1375,10 +1427,10 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
     </row>
   </sheetData>
@@ -1389,13 +1441,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C2F300-0ACE-414A-85D4-FE4A0E362995}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -1404,7 +1456,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1412,7 +1464,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1420,7 +1472,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -1428,7 +1480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -1437,7 +1489,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1445,7 +1497,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1454,7 +1506,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -1463,7 +1515,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -1479,14 +1531,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBBB7C2-660D-4F66-9443-9DB0EA674324}">
-  <dimension ref="A3:B8"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="49.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1495,7 +1552,7 @@
         <v>Sweden</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1504,7 +1561,7 @@
         <v>TARGET</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -1512,24 +1569,58 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="str">
-        <f>_xll.qlCalendarJointCalendar(B3,B4,B6)</f>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="str">
+        <f>_xll.qlCalendarJointCalendar(B3,B4,B8)</f>
         <v>JoinHolidays(Sweden, TARGET)</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" t="str">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="str">
         <f>_xll.qlCalendarJointCalendar2(B3,B4,B5)</f>
         <v>JoinHolidays(Sweden, TARGET, UK settlement)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="str" cm="1">
+        <f t="array" ref="B11">_xll.qlCalendarJointCalendar3(B3,B4,B5,B6,B8)</f>
+        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="str" cm="1">
+        <f t="array" ref="B12">_xll.qlCalendarJointCalendarN(B3:B7,B8)</f>
+        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark, Iceland stock exchange)</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_calendars.xlsx
+++ b/tests/workbooktests/workbooks/test_calendars.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9690DD57-097D-4671-A599-AB72DE620844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DBF0AE-5AA8-4EA2-90D2-68D38171C085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="types" sheetId="1" r:id="rId1"/>
     <sheet name="functions" sheetId="2" r:id="rId2"/>
-    <sheet name="addremove holidays" sheetId="6" r:id="rId3"/>
-    <sheet name="adjust , advance" sheetId="7" r:id="rId4"/>
-    <sheet name="joined calendar" sheetId="8" r:id="rId5"/>
+    <sheet name="addremove_holidays" sheetId="6" r:id="rId3"/>
+    <sheet name="adjust_advance" sheetId="7" r:id="rId4"/>
+    <sheet name="jointCalendar" sheetId="8" r:id="rId5"/>
+    <sheet name="bespokeCalendar" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
   <si>
     <t>ARGENTINA</t>
   </si>
@@ -292,46 +293,58 @@
     <t>calender_rule</t>
   </si>
   <si>
+    <t>qlCalender</t>
+  </si>
+  <si>
+    <t>UK_SETTLEMENT</t>
+  </si>
+  <si>
+    <t>US_SETTLEMENT</t>
+  </si>
+  <si>
+    <t>US_FEDERALRESERVE</t>
+  </si>
+  <si>
+    <t>US_SOFR</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar2</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendar3</t>
+  </si>
+  <si>
+    <t>qlCalendarJointCalendarN</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>qlBespokeCalendar</t>
+  </si>
+  <si>
+    <t>TestCalendar</t>
+  </si>
+  <si>
+    <t>qlBespokeCalendarAddWeekend</t>
+  </si>
+  <si>
+    <t>weekday</t>
+  </si>
+  <si>
+    <t>SATURDAY</t>
+  </si>
+  <si>
+    <t>SUNDAY</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
     <t>JOINHOLIDAYS</t>
-  </si>
-  <si>
-    <t>qlCalender</t>
-  </si>
-  <si>
-    <t>UK_Settlement</t>
-  </si>
-  <si>
-    <t>UK_SETTLEMENT</t>
-  </si>
-  <si>
-    <t>US_SETTLEMENT</t>
-  </si>
-  <si>
-    <t>US_FEDERALRESERVE</t>
-  </si>
-  <si>
-    <t>US_SOFR</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Iceland</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>qlCalendarJointCalendar</t>
-  </si>
-  <si>
-    <t>qlCalendarJointCalendar2</t>
-  </si>
-  <si>
-    <t>qlCalendarJointCalendar3</t>
-  </si>
-  <si>
-    <t>qlCalendarJointCalendarN</t>
   </si>
 </sst>
 </file>
@@ -375,11 +388,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -699,6 +719,7 @@
   <cols>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
@@ -1090,7 +1111,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C47" t="str">
         <f>_xll.qlCalendar(B47)</f>
@@ -1099,7 +1120,7 @@
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C48" t="str">
         <f>_xll.qlCalendar(B48)</f>
@@ -1108,7 +1129,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C49" t="str">
         <f>_xll.qlCalendar(B49)</f>
@@ -1117,7 +1138,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C50" t="str">
         <f>_xll.qlCalendar(B50)</f>
@@ -1136,14 +1157,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="4" t="str">
         <f>_xll.qlCalendar("TARGET")</f>
         <v>TARGET</v>
       </c>
@@ -1152,7 +1173,7 @@
       <c r="A2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="5">
         <v>46171</v>
       </c>
     </row>
@@ -1160,7 +1181,7 @@
       <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="4" t="str">
         <f>_xll.qlDateWeekday(B2)</f>
         <v>FRIDAY</v>
       </c>
@@ -1169,7 +1190,7 @@
       <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="5">
         <v>46023</v>
       </c>
     </row>
@@ -1177,7 +1198,7 @@
       <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="5">
         <v>46027</v>
       </c>
       <c r="D5" s="1">
@@ -1198,7 +1219,7 @@
       <c r="A7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="b">
+      <c r="B7" s="4" t="b">
         <f>_xll.qlCalendarisWeekend($B$1,B3)</f>
         <v>0</v>
       </c>
@@ -1207,7 +1228,7 @@
       <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="5">
         <f>_xll.qlCalendarStartOfMonth(B1,B2)</f>
         <v>46146</v>
       </c>
@@ -1216,7 +1237,7 @@
       <c r="A9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="5">
         <f>_xll.qlCalendarEndOfMonth(B1,B2)</f>
         <v>46171</v>
       </c>
@@ -1225,7 +1246,7 @@
       <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B10" t="b">
+      <c r="B10" s="4" t="b">
         <f>_xll.qlCalendarIsBusinessDay(B1,B2)</f>
         <v>1</v>
       </c>
@@ -1234,7 +1255,7 @@
       <c r="A11" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="b">
+      <c r="B11" s="4" t="b">
         <f>_xll.qlCalendarIsHoliday(B1,B2)</f>
         <v>0</v>
       </c>
@@ -1243,7 +1264,7 @@
       <c r="A12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" t="b">
+      <c r="B12" s="4" t="b">
         <f>_xll.qlCalendarIsEndOfMonth(B1,B2)</f>
         <v>1</v>
       </c>
@@ -1252,7 +1273,7 @@
       <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" t="b">
+      <c r="B13" s="4" t="b">
         <f>_xll.qlCalendarIsStartOfMonth(B1,B2)</f>
         <v>0</v>
       </c>
@@ -1261,7 +1282,7 @@
       <c r="A14" t="s">
         <v>53</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <f>_xll.qlCalendarBusinessDaysBetween(B1,B4,B5)</f>
         <v>1</v>
       </c>
@@ -1270,7 +1291,7 @@
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15" s="4" t="str">
         <f>_xll.qlCalendarName(B1)</f>
         <v>TARGET</v>
       </c>
@@ -1279,7 +1300,7 @@
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B16" t="b">
+      <c r="B16" s="4" t="b">
         <f>_xll.qlCalendarEmpty(B1)</f>
         <v>0</v>
       </c>
@@ -1288,7 +1309,7 @@
       <c r="A18" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="5">
         <f>_xll.qlCalendarHolidayList(B1,B4,B5)</f>
         <v>46023</v>
       </c>
@@ -1297,7 +1318,7 @@
       <c r="A19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="5">
         <f>TRANSPOSE(_xll.qlCalendarBusinessDayList(B1,B4,B5))</f>
         <v>46024</v>
       </c>
@@ -1310,32 +1331,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41849B37-CA87-4E4A-8B76-B839138C7508}">
-  <dimension ref="A2:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
+        <v>62</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46024</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1">
-        <v>46024</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>46023</v>
@@ -1343,95 +1372,87 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>46023</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1">
-        <v>46027</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="1">
-        <f>_xll.qlCalendarHolidayList(B2,B5,B6,B2)</f>
+        <f>_xll.qlCalendarHolidayList(B1,B4,B5,B1)</f>
         <v>46023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="b">
+        <f>_xll.qlCalendarAddHoliday(B1,B2,B6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" t="b">
-        <f>_xll.qlCalendarAddHoliday(B2,B3,B7)</f>
+        <v>54</v>
+      </c>
+      <c r="B9" s="1">
+        <f>TRANSPOSE(_xll.qlCalendarHolidayList(B1,B4,B5,B8))</f>
+        <v>46023</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="b">
+        <f>_xll.qlCalendarRemoveHoliday(B1,B3,B9)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="1">
-        <f>TRANSPOSE(_xll.qlCalendarHolidayList(B2,B5,B6,B9))</f>
-        <v>46023</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" t="b">
-        <f>_xll.qlCalendarRemoveHoliday(B2,B4,B10)</f>
+        <v>54</v>
+      </c>
+      <c r="B12" s="1">
+        <f>_xll.qlCalendarHolidayList(B1,B4,B5,B11)</f>
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="b">
+        <f>_xll.qlCalendarResetAddedAndRemovedHolidays(B1,B12)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="1">
-        <f>_xll.qlCalendarHolidayList(B2,B5,B6,B12)</f>
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="b">
-        <f>_xll.qlCalendarResetAddedAndRemovedHolidays(B2,B13)</f>
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="B15" s="1">
+        <f>_xll.qlCalendarHolidayList(B1,B4,B5,B14)</f>
+        <v>46023</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="1">
-        <f>_xll.qlCalendarHolidayList(B2,B5,B6,B15)</f>
-        <v>46023</v>
-      </c>
+      <c r="B16" s="1"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1531,7 +1552,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBBB7C2-660D-4F66-9443-9DB0EA674324}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1539,92 +1560,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>84</v>
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="str">
+        <f>_xll.qlCalendar("Sweden")</f>
+        <v>Sweden</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="str">
+        <f>_xll.qlCalendar("TARGET")</f>
+        <v>TARGET</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" t="str">
-        <f>_xll.qlCalendar("Sweden")</f>
-        <v>Sweden</v>
+        <v>75</v>
+      </c>
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3">_xll.qlCalendar("UK_Settlement")</f>
+        <v>UK settlement</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" t="str">
-        <f>_xll.qlCalendar("TARGET")</f>
-        <v>TARGET</v>
+        <v>75</v>
+      </c>
+      <c r="B4" t="str" cm="1">
+        <f t="array" ref="B4">_xll.qlCalendar("Denmark")</f>
+        <v>Denmark</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="B5" t="str" cm="1">
+        <f t="array" ref="B5">_xll.qlCalendar("Iceland")</f>
+        <v>Iceland stock exchange</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>83</v>
+      <c r="A7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="str">
+        <f>_xll.qlCalendarJointCalendar(B1,B2,B6)</f>
+        <v>JoinHolidays(Sweden, TARGET)</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
+      <c r="A8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="str">
+        <f>_xll.qlCalendarJointCalendar2(B1,B2,B3)</f>
+        <v>JoinHolidays(Sweden, TARGET, UK settlement)</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="str">
-        <f>_xll.qlCalendarJointCalendar(B3,B4,B8)</f>
-        <v>JoinHolidays(Sweden, TARGET)</v>
+        <v>82</v>
+      </c>
+      <c r="B9" t="str" cm="1">
+        <f t="array" ref="B9">_xll.qlCalendarJointCalendar3(B1,B2,B3,B4,B6)</f>
+        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark)</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="str">
-        <f>_xll.qlCalendarJointCalendar2(B3,B4,B5)</f>
-        <v>JoinHolidays(Sweden, TARGET, UK settlement)</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlCalendarJointCalendar3(B3,B4,B5,B6,B8)</f>
-        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark)</v>
+        <v>83</v>
+      </c>
+      <c r="B10" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlCalendarJointCalendarN(B1:B5,B6)</f>
+        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark, Iceland stock exchange)</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B12" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlCalendarJointCalendarN(B3:B7,B8)</f>
-        <v>JoinHolidays(Sweden, TARGET, UK settlement, Denmark, Iceland stock exchange)</v>
+      <c r="B12" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="b" cm="1">
+        <f t="array" ref="B13">_xll.qlCalendarisWeekend(B7,B12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="4" t="b" cm="1">
+        <f t="array" ref="B15">_xll.qlCalendarisWeekend(B7,B14)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9414356-29FD-43C6-BF7E-7BF23ACAB286}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="str" cm="1">
+        <f t="array" ref="B2">_xll.qlBespokeCalendar(B1)</f>
+        <v>BESPOKECALENDAR(TestCalendar)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="4" t="b" cm="1">
+        <f t="array" ref="B4">_xll.qlBespokeCalendarAddWeekend(B2,B3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="b" cm="1">
+        <f t="array" ref="B6">_xll.qlCalendarisWeekend(B2,B5,B4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="b" cm="1">
+        <f t="array" ref="B8">_xll.qlCalendarisWeekend(B2,B7,B6)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/workbooktests/workbooks/test_calendars.xlsx
+++ b/tests/workbooktests/workbooks/test_calendars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DBF0AE-5AA8-4EA2-90D2-68D38171C085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B74D59-AA4D-4FBB-9FFB-C0A433F50908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93E3CEBE-2A7E-45F9-A944-9E4960940BAD}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="117">
   <si>
     <t>ARGENTINA</t>
   </si>
@@ -345,6 +345,78 @@
   </si>
   <si>
     <t>JOINHOLIDAYS</t>
+  </si>
+  <si>
+    <t>CROATIA</t>
+  </si>
+  <si>
+    <t>MALTA</t>
+  </si>
+  <si>
+    <t>MONTENEGRO</t>
+  </si>
+  <si>
+    <t>NORTHMACEDONIA</t>
+  </si>
+  <si>
+    <t>SERBIA</t>
+  </si>
+  <si>
+    <t>SLOVENIA</t>
+  </si>
+  <si>
+    <t>UZBEKISTAN</t>
+  </si>
+  <si>
+    <t>qlCalendarAddedHolidays</t>
+  </si>
+  <si>
+    <t>qlCalendarRemovedHolidays</t>
+  </si>
+  <si>
+    <t>BRAZIL_EXCHANGE</t>
+  </si>
+  <si>
+    <t>CANADA_TSX</t>
+  </si>
+  <si>
+    <t>CHINA_IB</t>
+  </si>
+  <si>
+    <t>FRANCE_EXCHANGE</t>
+  </si>
+  <si>
+    <t>GERMANY_SETTLEMENT</t>
+  </si>
+  <si>
+    <t>GERMANY_EUREX</t>
+  </si>
+  <si>
+    <t>GERMANY_XETRA</t>
+  </si>
+  <si>
+    <t>ISRAEL_TELBOR</t>
+  </si>
+  <si>
+    <t>ISRAEL_SHIR</t>
+  </si>
+  <si>
+    <t>ISRAEL_TASE</t>
+  </si>
+  <si>
+    <t>ITALY_EXCHANGE</t>
+  </si>
+  <si>
+    <t>NEWZEALAND_AUCKLAND</t>
+  </si>
+  <si>
+    <t>POLAND_WSE</t>
+  </si>
+  <si>
+    <t>RUSSIA_MOEX</t>
+  </si>
+  <si>
+    <t>SOUTHKOREA_SETTLEMENT</t>
   </si>
 </sst>
 </file>
@@ -388,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -400,6 +472,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -714,9 +787,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3075420B-A904-48C0-8CC0-21FB5C882A54}">
-  <dimension ref="B2:C50"/>
+  <dimension ref="A2:C72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.5703125" style="2"/>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
     <col min="4" max="4" width="33.7109375" customWidth="1"/>
@@ -769,379 +843,577 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="C7" t="str">
         <f>_xll.qlCalendar(B7)</f>
-        <v>Canada</v>
+        <v>BOVESPA</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="str">
         <f>_xll.qlCalendar(B8)</f>
-        <v>Santiago Stock Exchange</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="C9" t="str">
         <f>_xll.qlCalendar(B9)</f>
-        <v>Shanghai stock exchange</v>
+        <v>TSX</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" t="str">
         <f>_xll.qlCalendar(B10)</f>
-        <v>Prague stock exchange</v>
+        <v>Santiago Stock Exchange</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="str">
         <f>_xll.qlCalendar(B11)</f>
-        <v>Denmark</v>
+        <v>Shanghai stock exchange</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="C12" t="str">
         <f>_xll.qlCalendar(B12)</f>
-        <v>Finland</v>
+        <v>China inter bank market</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" t="str">
         <f>_xll.qlCalendar(B13)</f>
-        <v>French settlement</v>
+        <v>Prague stock exchange</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C14" t="str">
         <f>_xll.qlCalendar(B14)</f>
-        <v>Frankfurt stock exchange</v>
+        <v>Zagreb stock exchange</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C15" t="str">
         <f>_xll.qlCalendar(B15)</f>
-        <v>Hong Kong stock exchange</v>
+        <v>Denmark</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C16" t="str">
         <f>_xll.qlCalendar(B16)</f>
-        <v>Hungary</v>
+        <v>Finland</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C17" t="str">
         <f>_xll.qlCalendar(B17)</f>
-        <v>Iceland stock exchange</v>
+        <v>French settlement</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="C18" t="str">
         <f>_xll.qlCalendar(B18)</f>
-        <v>National Stock Exchange of India</v>
+        <v>Paris stock exchange</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C19" t="str">
         <f>_xll.qlCalendar(B19)</f>
-        <v>Jakarta stock exchange</v>
+        <v>Frankfurt stock exchange</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="C20" t="str">
         <f>_xll.qlCalendar(B20)</f>
-        <v>Tel Aviv stock exchange</v>
+        <v>German settlement</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="C21" t="str">
         <f>_xll.qlCalendar(B21)</f>
-        <v>Italian settlement</v>
+        <v>Eurex</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="C22" t="str">
         <f>_xll.qlCalendar(B22)</f>
-        <v>Japan</v>
+        <v>Xetra</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C23" t="str">
         <f>_xll.qlCalendar(B23)</f>
-        <v>Mexican stock exchange</v>
+        <v>Hong Kong stock exchange</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C24" t="str">
         <f>_xll.qlCalendar(B24)</f>
-        <v>New Zealand (Wellington)</v>
+        <v>Hungary</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C25" t="str">
         <f>_xll.qlCalendar(B25)</f>
-        <v>Norway</v>
+        <v>Iceland stock exchange</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C26" t="str">
         <f>_xll.qlCalendar(B26)</f>
-        <v>Poland Settlement</v>
+        <v>National Stock Exchange of India</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C27" t="str">
         <f>_xll.qlCalendar(B27)</f>
-        <v>Bucharest stock exchange</v>
+        <v>Jakarta stock exchange</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C28" t="str">
         <f>_xll.qlCalendar(B28)</f>
-        <v>Russian settlement</v>
+        <v>Tel Aviv stock exchange</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C29" t="str">
         <f>_xll.qlCalendar(B29)</f>
-        <v>Tadawul</v>
+        <v>Tel Aviv stock exchange</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="C30" t="str">
         <f>_xll.qlCalendar(B30)</f>
-        <v>Singapore exchange</v>
+        <v>SHIR fixing calendar</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="C31" t="str">
         <f>_xll.qlCalendar(B31)</f>
-        <v>Bratislava stock exchange</v>
+        <v>Telbor fixing calendar</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C32" t="str">
         <f>_xll.qlCalendar(B32)</f>
-        <v>South Africa</v>
+        <v>Italian settlement</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="C33" t="str">
         <f>_xll.qlCalendar(B33)</f>
-        <v>South-Korea exchange</v>
+        <v>Milan stock exchange</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
         <f>_xll.qlCalendar(B34)</f>
-        <v>Sweden</v>
+        <v>Japan</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="C35" t="str">
         <f>_xll.qlCalendar(B35)</f>
-        <v>Switzerland</v>
+        <v>Malta Stock Exchange</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C36" t="str">
         <f>_xll.qlCalendar(B36)</f>
-        <v>Taiwan stock exchange</v>
+        <v>Mexican stock exchange</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="C37" t="str">
         <f>_xll.qlCalendar(B37)</f>
-        <v>TARGET</v>
+        <v>Montenegro Stock Exchange</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C38" t="str">
         <f>_xll.qlCalendar(B38)</f>
-        <v>Thailand stock exchange</v>
+        <v>New Zealand (Wellington)</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="C39" t="str">
         <f>_xll.qlCalendar(B39)</f>
-        <v>Turkey</v>
+        <v>New Zealand (Auckland)</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C40" t="str">
         <f>_xll.qlCalendar(B40)</f>
-        <v>Ukrainian stock exchange</v>
+        <v>Macedonian Stock Exchange</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>39</v>
+      <c r="B41" t="s">
+        <v>23</v>
       </c>
       <c r="C41" t="str">
         <f>_xll.qlCalendar(B41)</f>
-        <v>New York stock exchange</v>
+        <v>Norway</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C42" t="str">
         <f>_xll.qlCalendar(B42)</f>
-        <v>UK settlement</v>
+        <v>Poland Settlement</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="C43" t="str">
         <f>_xll.qlCalendar(B43)</f>
-        <v>Null</v>
+        <v>Warsaw stock exchange</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C44" t="str">
         <f>_xll.qlCalendar(B44)</f>
-        <v>weekends only</v>
+        <v>Bucharest stock exchange</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="str">
+        <f>_xll.qlCalendar(B45)</f>
+        <v>Russian settlement</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" t="str">
+        <f>_xll.qlCalendar(B46)</f>
+        <v>Moscow exchange</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C47" t="str">
         <f>_xll.qlCalendar(B47)</f>
-        <v>UK settlement</v>
+        <v>Tadawul</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C48" t="str">
         <f>_xll.qlCalendar(B48)</f>
-        <v>US settlement</v>
+        <v>Belgrade stock exchange</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C49" t="str">
         <f>_xll.qlCalendar(B49)</f>
-        <v>Federal Reserve Bankwire System</v>
+        <v>Singapore exchange</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C50" t="str">
         <f>_xll.qlCalendar(B50)</f>
+        <v>Bratislava stock exchange</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="str">
+        <f>_xll.qlCalendar(B51)</f>
+        <v>Ljubljana stock exchange</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="str">
+        <f>_xll.qlCalendar(B52)</f>
+        <v>South Africa</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="str">
+        <f>_xll.qlCalendar(B53)</f>
+        <v>South-Korea exchange</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="str">
+        <f>_xll.qlCalendar(B54)</f>
+        <v>South-Korean settlement</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="str">
+        <f>_xll.qlCalendar(B55)</f>
+        <v>Sweden</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" t="str">
+        <f>_xll.qlCalendar(B56)</f>
+        <v>Switzerland</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" t="str">
+        <f>_xll.qlCalendar(B57)</f>
+        <v>Taiwan stock exchange</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" t="str">
+        <f>_xll.qlCalendar(B58)</f>
+        <v>TARGET</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" t="str">
+        <f>_xll.qlCalendar(B59)</f>
+        <v>Thailand stock exchange</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" t="str">
+        <f>_xll.qlCalendar(B60)</f>
+        <v>Turkey</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="str">
+        <f>_xll.qlCalendar(B61)</f>
+        <v>Ukrainian stock exchange</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" t="str">
+        <f>_xll.qlCalendar(B62)</f>
+        <v>New York stock exchange</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" t="str">
+        <f>_xll.qlCalendar(B63)</f>
+        <v>UK settlement</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" t="str">
+        <f>_xll.qlCalendar(B64)</f>
+        <v>Uzbekistan Stock Exchange</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" t="str">
+        <f>_xll.qlCalendar(B65)</f>
+        <v>Null</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>42</v>
+      </c>
+      <c r="C66" t="str">
+        <f>_xll.qlCalendar(B66)</f>
+        <v>weekends only</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" t="str">
+        <f>_xll.qlCalendar(B69)</f>
+        <v>UK settlement</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" t="str">
+        <f>_xll.qlCalendar(B70)</f>
+        <v>US settlement</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" t="str">
+        <f>_xll.qlCalendar(B71)</f>
+        <v>Federal Reserve Bankwire System</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" t="str">
+        <f>_xll.qlCalendar(B72)</f>
         <v>SOFR fixing calendar</v>
       </c>
     </row>
@@ -1320,7 +1592,7 @@
       </c>
       <c r="B19" s="5">
         <f>TRANSPOSE(_xll.qlCalendarBusinessDayList(B1,B4,B5))</f>
-        <v>46024</v>
+        <v>46027</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1603,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41849B37-CA87-4E4A-8B76-B839138C7508}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.42578125" customWidth="1"/>
@@ -1432,27 +1704,63 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="b">
-        <f>_xll.qlCalendarResetAddedAndRemovedHolidays(B1,B12)</f>
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="B14" s="1" cm="1">
+        <f t="array" ref="B14">_xll.qlCalendarAddedHolidays(B1,B8)</f>
+        <v>46024</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="1">
-        <f>_xll.qlCalendarHolidayList(B1,B4,B5,B14)</f>
+        <v>101</v>
+      </c>
+      <c r="B15" s="1" cm="1">
+        <f t="array" ref="B15">_xll.qlCalendarRemovedHolidays(B1,B11)</f>
         <v>46023</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="7" t="b">
+        <f>_xll.qlCalendarResetAddedAndRemovedHolidays(B1,B15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="1">
+        <f>_xll.qlCalendarHolidayList(B1,B4,B5,B17)</f>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="1" cm="1">
+        <f t="array" ref="B20">_xll.qlCalendarAddedHolidays(B1,B17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="1" cm="1">
+        <f t="array" ref="B21">_xll.qlCalendarRemovedHolidays(B1,B17)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
